--- a/data/trans_dic/P36BPD07_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD07_R-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,21; 93,4</t>
+          <t>89,09; 93,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,42; 76,98</t>
+          <t>70,77; 77,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,42; 95,66</t>
+          <t>92,47; 95,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75,74; 80,39</t>
+          <t>74,65; 79,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,68; 94,23</t>
+          <t>91,63; 94,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,23; 78,27</t>
+          <t>73,87; 78,14</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,16; 82,59</t>
+          <t>79,21; 82,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,03; 81,39</t>
+          <t>65,21; 69,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,95; 84,33</t>
+          <t>80,75; 84,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74,16; 83,52</t>
+          <t>71,57; 75,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,45; 82,93</t>
+          <t>80,51; 82,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,83; 79,82</t>
+          <t>68,95; 72,03</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,71; 90,22</t>
+          <t>84,94; 90,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,59; 83,49</t>
+          <t>77,98; 84,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,63; 90,78</t>
+          <t>85,77; 90,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81,52; 86,64</t>
+          <t>80,52; 85,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,05; 89,83</t>
+          <t>86,17; 89,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,54; 84,45</t>
+          <t>80,29; 84,34</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,11; 85,57</t>
+          <t>82,97; 85,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,26; 80,19</t>
+          <t>69,6; 73,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,58; 87,8</t>
+          <t>85,49; 87,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76,94; 82,57</t>
+          <t>74,9; 77,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,76; 86,57</t>
+          <t>84,79; 86,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,59; 79,85</t>
+          <t>72,83; 74,99</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>375338</t>
+          <t>428348</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>590708</t>
+          <t>635637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>966046</t>
+          <t>1063986</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>664817; 696005</t>
+          <t>663898; 695798</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>356041; 394833</t>
+          <t>407914; 448288</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>910236; 942182</t>
+          <t>910719; 940794</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>572220; 607330</t>
+          <t>613652; 654709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1586232; 1630316</t>
+          <t>1585307; 1626822</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>941536; 992805</t>
+          <t>1033066; 1092689</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1651225</t>
+          <t>1504831</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1733945</t>
+          <t>1590934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3385170</t>
+          <t>3095765</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1635033; 1705809</t>
+          <t>1636060; 1706791</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1556257; 1861818</t>
+          <t>1452632; 1554756</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1600272; 1667140</t>
+          <t>1596436; 1661750</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1656477; 1865420</t>
+          <t>1550456; 1633139</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3251857; 3352245</t>
+          <t>3254454; 3351428</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3247355; 3608655</t>
+          <t>3029565; 3164882</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518837</t>
+          <t>578051</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>554253</t>
+          <t>611963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1073091</t>
+          <t>1190014</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>460624; 490591</t>
+          <t>461889; 491904</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>488756; 539862</t>
+          <t>554872; 599716</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>469238; 497469</t>
+          <t>470021; 498471</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>537435; 571207</t>
+          <t>590164; 629158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>939502; 980756</t>
+          <t>940812; 980729</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1038734; 1102779</t>
+          <t>1159862; 1218337</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2545401</t>
+          <t>2511231</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2878906</t>
+          <t>2838534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5424306</t>
+          <t>5349765</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2787944; 2870258</t>
+          <t>2783047; 2870702</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2456402; 2764129</t>
+          <t>2446925; 2566911</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3003592; 3081555</t>
+          <t>3000692; 3079557</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2807040; 3012357</t>
+          <t>2787246; 2884112</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5818016; 5942108</t>
+          <t>5819945; 5932727</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5292241; 5665682</t>
+          <t>5270730; 5426754</t>
         </is>
       </c>
     </row>
